--- a/packages/calculators/src/modules/test/15.8-purchased-packaging.xlsx
+++ b/packages/calculators/src/modules/test/15.8-purchased-packaging.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5A931E-111A-4C4E-89BD-29ED58D826A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79486A03-7C30-3742-8F0C-ACE8E7F0D3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15.8.1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t/>
   </si>
@@ -84,6 +84,21 @@
   </si>
   <si>
     <t>Plastic crate polypropylene</t>
+  </si>
+  <si>
+    <t>Qp (units)</t>
+  </si>
+  <si>
+    <t>Qp (mass)</t>
+  </si>
+  <si>
+    <t>Corrugated board</t>
+  </si>
+  <si>
+    <t>Plastic film LDPE</t>
+  </si>
+  <si>
+    <t>Plastic sheet HDPE</t>
   </si>
 </sst>
 </file>
@@ -469,237 +484,331 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:G21"/>
+  <dimension ref="A4:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D5" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6">
         <v>468</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>469</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>1</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>2</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>3</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>8</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F8" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>6.04</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F9" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>3.41</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
         <v>100</v>
       </c>
-      <c r="C11">
-        <f xml:space="preserve"> _xlfn.XLOOKUP(A11, $F$8:$F$12,$G$8:$G$12)</f>
+      <c r="D11">
+        <f xml:space="preserve"> _xlfn.XLOOKUP(A11, $G$8:$G$12,$H$8:$H$12)</f>
         <v>6.04</v>
       </c>
-      <c r="D11">
-        <f>(B11 * C11)/1000</f>
+      <c r="E11">
+        <f>(B11 * D11)/1000</f>
         <v>0.60399999999999998</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>15</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>190.15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12">
         <v>123000</v>
       </c>
-      <c r="C12">
-        <f t="shared" ref="C12:C15" si="0" xml:space="preserve"> _xlfn.XLOOKUP(A12, $F$8:$F$12,$G$8:$G$12)</f>
+      <c r="D12">
+        <f t="shared" ref="D12:D15" si="0" xml:space="preserve"> _xlfn.XLOOKUP(A12, $G$8:$G$12,$H$8:$H$12)</f>
         <v>0.9</v>
       </c>
-      <c r="D12">
-        <f t="shared" ref="D12:D15" si="1">(B12 * C12)/1000</f>
+      <c r="E12">
+        <f t="shared" ref="E12:E15" si="1">(B12 * D12)/1000</f>
         <v>110.7</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>16</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>3.99</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <v>70</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <f t="shared" si="0"/>
         <v>3.41</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <f t="shared" si="1"/>
         <v>0.23870000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <v>50</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <f t="shared" si="0"/>
         <v>190.15</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <f t="shared" si="1"/>
         <v>9.5075000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <v>5750</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <f t="shared" si="0"/>
         <v>3.99</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <f t="shared" si="1"/>
         <v>22.942499999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17">
+        <v>255</v>
+      </c>
+      <c r="D17">
+        <f xml:space="preserve"> _xlfn.XLOOKUP(A17, $G$17:$G$19,$H$17:$H$19)</f>
+        <v>1.050716</v>
+      </c>
+      <c r="E17">
+        <f>C17*D17/1000</f>
+        <v>0.26793257999999998</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17">
+        <v>1.050716</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>1200</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ref="D18:D19" si="2" xml:space="preserve"> _xlfn.XLOOKUP(A18, $G$17:$G$19,$H$17:$H$19)</f>
+        <v>3.4411615000000002</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ref="E18:E19" si="3">C18*D18/1000</f>
+        <v>4.1293937999999999</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>3.4411615000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19">
+        <v>27</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>3.7225687000000001</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="3"/>
+        <v>0.1005093549</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19">
+        <v>3.7225687000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B19">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B23">
         <v>800</v>
       </c>
-      <c r="C19">
+      <c r="D23">
         <v>0.5</v>
       </c>
-      <c r="D19">
-        <f>(B19 * C19)/1000</f>
+      <c r="E23">
+        <f>(B23 * D23)/1000</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B20">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B24">
         <v>9000</v>
       </c>
-      <c r="C20">
+      <c r="D24">
         <v>2.3450000000000002</v>
       </c>
-      <c r="D20">
-        <f t="shared" ref="D20:D21" si="2">(B20 * C20)/1000</f>
+      <c r="E24">
+        <f t="shared" ref="E24:E25" si="4">(B24 * D24)/1000</f>
         <v>21.105</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B21">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B25">
         <v>10000</v>
       </c>
-      <c r="C21">
+      <c r="D25">
         <v>1.0009999999999999</v>
       </c>
-      <c r="D21">
-        <f t="shared" si="2"/>
+      <c r="E25">
+        <f t="shared" si="4"/>
         <v>10.009999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>57</v>
+      </c>
+      <c r="D27">
+        <v>2.5</v>
+      </c>
+      <c r="E27">
+        <f>C27*D27/1000</f>
+        <v>0.14249999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>2000</v>
+      </c>
+      <c r="D28">
+        <v>0.5</v>
+      </c>
+      <c r="E28">
+        <f>C28*D28/1000</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A7:D9 A5:C5 A6 D10" numberStoredAsText="1"/>
+    <ignoredError sqref="D7:E9 D5 A6 E10 A5:B5 A7:B9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/packages/calculators/src/modules/test/15.8-purchased-packaging.xlsx
+++ b/packages/calculators/src/modules/test/15.8-purchased-packaging.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79486A03-7C30-3742-8F0C-ACE8E7F0D3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
